--- a/scf_manager/data/reports/weekly_data_20260520.xlsx
+++ b/scf_manager/data/reports/weekly_data_20260520.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="发布概览" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="发布明细" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="监控数据" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="回滚明细" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="监控数据" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -458,7 +459,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -499,7 +500,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -561,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -622,141 +623,72 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>OLD-0001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>华为技术有限公司</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>通信-基站</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>常规放款迭代</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>全量发布</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2025-01-15 10:23</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2025-01-15 10:25</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2025-01-15 10:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>OLD-0002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>v2.1.0</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>比亚迪股份有限公司</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>新能源-电池</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>紧急资金故障</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>已回滚</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2025-03-20 14:30</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2025-03-20 14:31</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2025-03-20 00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BAD-0003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>v9.9.9</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>坏数据企业</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>测试</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>常规放款迭代</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>待前置检查</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>回滚ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>发布ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>企业</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>触发原因</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>回滚时间</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>报告路径</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
